--- a/wwwroot/CheckPrintTracking/Check_Print_Tracking_v1.xlsx
+++ b/wwwroot/CheckPrintTracking/Check_Print_Tracking_v1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TharakaJayam\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (5)\wwwroot\CheckPrintTracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12058000-5C86-438B-B1D1-F6C951629172}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AE7AC4-8449-4101-A9E1-D10FBBF5EB31}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="13224" windowHeight="5556" xr2:uid="{ADFA9B1B-1D26-41E7-8930-FB6B4836DFDE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Cheque Name/ Employee Name</t>
   </si>
@@ -34,6 +34,9 @@
   </si>
   <si>
     <t>Printed On</t>
+  </si>
+  <si>
+    <t>Amount</t>
   </si>
 </sst>
 </file>
@@ -385,15 +388,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{506B72BD-3933-4D8D-A752-4CE8B549228A}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -401,6 +405,9 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>

--- a/wwwroot/CheckPrintTracking/Check_Print_Tracking_v1.xlsx
+++ b/wwwroot/CheckPrintTracking/Check_Print_Tracking_v1.xlsx
@@ -2,19 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (5)\wwwroot\CheckPrintTracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AE7AC4-8449-4101-A9E1-D10FBBF5EB31}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7ED7E1-FCC1-40FA-B62B-68014B5AB006}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="13224" windowHeight="5556" xr2:uid="{ADFA9B1B-1D26-41E7-8930-FB6B4836DFDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$2</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>Cheque Name/ Employee Name</t>
   </si>
@@ -33,16 +36,28 @@
     <t>Date</t>
   </si>
   <si>
+    <t>Amount</t>
+  </si>
+  <si>
     <t>Printed On</t>
   </si>
   <si>
-    <t>Amount</t>
+    <t>CASH</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -72,8 +87,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -388,13 +406,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{506B72BD-3933-4D8D-A752-4CE8B549228A}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -405,13 +423,43 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>10000</v>
+      </c>
+      <c r="D2" s="2">
+        <v>46253.886458333298</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3">
+        <v>10000</v>
+      </c>
+      <c r="D3" s="2">
+        <v>46253.889780092592</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/wwwroot/CheckPrintTracking/Check_Print_Tracking_v1.xlsx
+++ b/wwwroot/CheckPrintTracking/Check_Print_Tracking_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (5)\wwwroot\CheckPrintTracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7ED7E1-FCC1-40FA-B62B-68014B5AB006}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9363B95F-AF7C-4DDF-9E9E-E7D6C1E5104F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="13224" windowHeight="5556" xr2:uid="{ADFA9B1B-1D26-41E7-8930-FB6B4836DFDE}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
   <si>
     <t>Cheque Name/ Employee Name</t>
   </si>
@@ -55,8 +55,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -87,11 +88,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -406,13 +409,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{506B72BD-3933-4D8D-A752-4CE8B549228A}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -440,7 +443,7 @@
         <v>10000</v>
       </c>
       <c r="D2" s="2">
-        <v>46253.886458333298</v>
+        <v>46253.886458333334</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -450,11 +453,39 @@
       <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="1">
         <v>10000</v>
       </c>
       <c r="D3" s="2">
-        <v>46253.889780092592</v>
+        <v>46253.889780092599</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46254.028807870367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46252</v>
+      </c>
+      <c r="C5" s="4">
+        <v>10000</v>
+      </c>
+      <c r="D5" s="5">
+        <v>46254.032118055555</v>
       </c>
     </row>
   </sheetData>

--- a/wwwroot/CheckPrintTracking/Check_Print_Tracking_v1.xlsx
+++ b/wwwroot/CheckPrintTracking/Check_Print_Tracking_v1.xlsx
@@ -1,115 +1,147 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <x:workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (5)\wwwroot\CheckPrintTracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9363B95F-AF7C-4DDF-9E9E-E7D6C1E5104F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13224" windowHeight="5556" xr2:uid="{ADFA9B1B-1D26-41E7-8930-FB6B4836DFDE}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$2</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A745A1F2-B843-420D-B908-63FB0D485118}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <x:bookViews>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="13224" windowHeight="5556" firstSheet="0" activeTab="0" xr2:uid="{ADFA9B1B-1D26-41E7-8930-FB6B4836DFDE}"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </x:sheets>
+  <x:definedNames>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1</x:definedName>
+  </x:definedNames>
+  <x:calcPr calcId="191029"/>
+  <x:extLst>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
-</workbook>
+    </x:ext>
+  </x:extLst>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
-  <si>
-    <t>Cheque Name/ Employee Name</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>Printed On</t>
-  </si>
-  <si>
-    <t>CASH</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-</sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:si>
+    <x:t>Cheque Name/ Employee Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Date</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Printed On</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASH</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
-    <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss\ AM/PM"/>
-  </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2 xr">
+  <x:numFmts count="5">
+    <x:numFmt numFmtId="164" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+    <x:numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss\ AM/PM"/>
+    <x:numFmt numFmtId="166" formatCode="M/d/yyyy"/>
+    <x:numFmt numFmtId="167" formatCode="#,##0.00"/>
+    <x:numFmt numFmtId="168" formatCode="M/d/yyyy h:mm:ss AM/PM"/>
+  </x:numFmts>
+  <x:fonts count="2" x14ac:knownFonts="1">
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="2">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+  </x:fills>
+  <x:borders count="1">
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs count="7">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+  </x:cellStyleXfs>
+  <x:cellXfs count="8">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <x:xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </x:cellStyles>
+  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <x:extLst>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+    </x:ext>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
-</styleSheet>
+    </x:ext>
+  </x:extLst>
+</x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -408,89 +440,60 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{506B72BD-3933-4D8D-A752-4CE8B549228A}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="31.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" style="2" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1">
-        <v>10000</v>
-      </c>
-      <c r="D2" s="2">
-        <v>46253.886458333334</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1">
-        <v>10000</v>
-      </c>
-      <c r="D3" s="2">
-        <v>46253.889780092599</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1">
-        <v>10000</v>
-      </c>
-      <c r="D4" s="2">
-        <v>46254.028807870367</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3">
-        <v>46252</v>
-      </c>
-      <c r="C5" s="4">
-        <v>10000</v>
-      </c>
-      <c r="D5" s="5">
-        <v>46254.032118055555</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{506B72BD-3933-4D8D-A752-4CE8B549228A}" mc:Ignorable="x14ac xr xr2 xr3">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:D4"/>
+  <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <x:cols>
+    <x:col min="1" max="1" width="31.853482" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="9.996339" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="3" max="3" width="10.567768" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="4" width="21.567768" style="2" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <x:c r="A1" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <x:c r="A2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B2" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C2" s="6">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="D2" s="7">
+        <x:v>46254.0413614815</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <x:c r="C3" s="1"/>
+    </x:row>
+    <x:row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <x:c r="B4" s="3"/>
+      <x:c r="C4" s="1"/>
+    </x:row>
+  </x:sheetData>
+  <x:autoFilter ref="A1:D1"/>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" r:id="rId1"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/wwwroot/CheckPrintTracking/Check_Print_Tracking_v1.xlsx
+++ b/wwwroot/CheckPrintTracking/Check_Print_Tracking_v1.xlsx
@@ -43,6 +43,258 @@
   </x:si>
   <x:si>
     <x:t>CASH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tharaka Jayampathi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kasun Jaya</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test Tharaka One</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Saman Perera</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kasun Silva</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sachin Fernando</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amal Fernando</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gihan Perera</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sachin Gunawardena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tharindu Jayasuriya</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dinesh Herath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ruwan Jayasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Saman Fernando</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pradeep Kumarasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Janith Senanayake</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ravindu Fernando</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gihan Karunaratne</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Chamara Herath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kasun Jayasuriya</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kasun Wickramasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Janith Rajapaksha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pradeep Wijesinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kamal Kumarasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sachin Jayasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nimal Jayasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dilshan Gunawardena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Roshan Karunaratne</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lahiru Gunawardena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Janith Silva</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sachin Senanayake</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandun Karunaratne</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nimal Wickramasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dinesh Jayasuriya</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kamal Gunawardena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amal Rajapaksha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sachin Jayasuriya</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dilshan Fernando</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Janith Perera</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tharindu Senanayake</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Saman Wickramasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Supun Kumarasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dinesh Senanayake</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Supun Karunaratne</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lahiru Perera</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Isuru Jayasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Roshan Fernando</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kamal Jayasuriya</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ruwan Rajapaksha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dinesh Bandara</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandun Jayasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pradeep Ranatunga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Saman Jayasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amal Kumarasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kasun Perera</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lahiru Jayasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Roshan Kumarasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lahiru Jayasuriya</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Saman Rajapaksha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandun Ranatunga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Janith Jayasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Janith Jayasuriya</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Chamara Wickramasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dinesh Gunawardena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tharindu Karunaratne</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Isuru Gunawardena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sachin Rajapaksha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Chamara Bandara</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Roshan Herath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dilshan Perera</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nimal Senanayake</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kasun Gunawardena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Roshan Jayasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gihan Fernando</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Roshan Senanayake</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Chamara Rajapaksha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tharindu Gunawardena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Isuru Ranatunga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kamal Perera</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Supun Bandara</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kamal Karunaratne</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dinesh Ranatunga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Isuru Kumarasinghe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Saman Karunaratne</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Saman Herath</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -449,7 +701,7 @@
   <x:cols>
     <x:col min="1" max="1" width="31.853482" style="0" bestFit="1" customWidth="1"/>
     <x:col min="2" max="2" width="9.996339" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="3" max="3" width="10.567768" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="3" max="3" width="11.996339" style="0" bestFit="1" customWidth="1"/>
     <x:col min="4" max="4" width="21.567768" style="2" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -482,11 +734,1404 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <x:c r="C3" s="1"/>
+      <x:c r="A3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B3" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C3" s="6">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="D3" s="7">
+        <x:v>46254.0660858912</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <x:c r="B4" s="3"/>
-      <x:c r="C4" s="1"/>
+      <x:c r="A4" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B4" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C4" s="6">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="D4" s="7">
+        <x:v>46254.0660933102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:4">
+      <x:c r="A5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B5" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C5" s="6">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D5" s="7">
+        <x:v>46254.0660940162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:4">
+      <x:c r="A6" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B6" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C6" s="6">
+        <x:v>825812.93</x:v>
+      </x:c>
+      <x:c r="D6" s="7">
+        <x:v>46254.0660946065</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:4">
+      <x:c r="A7" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B7" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C7" s="6">
+        <x:v>308383.03</x:v>
+      </x:c>
+      <x:c r="D7" s="7">
+        <x:v>46254.0660952199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:4">
+      <x:c r="A8" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B8" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C8" s="6">
+        <x:v>1266343.54</x:v>
+      </x:c>
+      <x:c r="D8" s="7">
+        <x:v>46254.0660959259</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:4">
+      <x:c r="A9" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B9" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C9" s="6">
+        <x:v>698750.02</x:v>
+      </x:c>
+      <x:c r="D9" s="7">
+        <x:v>46254.0660964236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:4">
+      <x:c r="A10" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B10" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C10" s="6">
+        <x:v>597314.11</x:v>
+      </x:c>
+      <x:c r="D10" s="7">
+        <x:v>46254.066097037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:4">
+      <x:c r="A11" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B11" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C11" s="6">
+        <x:v>1348177.93</x:v>
+      </x:c>
+      <x:c r="D11" s="7">
+        <x:v>46254.0660976505</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:4">
+      <x:c r="A12" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B12" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C12" s="6">
+        <x:v>20489.78</x:v>
+      </x:c>
+      <x:c r="D12" s="7">
+        <x:v>46254.0660982523</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:4">
+      <x:c r="A13" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B13" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C13" s="6">
+        <x:v>1021411.3</x:v>
+      </x:c>
+      <x:c r="D13" s="7">
+        <x:v>46254.0660988542</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:4">
+      <x:c r="A14" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B14" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C14" s="6">
+        <x:v>2290718.89</x:v>
+      </x:c>
+      <x:c r="D14" s="7">
+        <x:v>46254.066099537</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:4">
+      <x:c r="A15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B15" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C15" s="6">
+        <x:v>291052.41</x:v>
+      </x:c>
+      <x:c r="D15" s="7">
+        <x:v>46254.0661001505</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:4">
+      <x:c r="A16" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B16" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C16" s="6">
+        <x:v>2421577.69</x:v>
+      </x:c>
+      <x:c r="D16" s="7">
+        <x:v>46254.0661008796</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:4">
+      <x:c r="A17" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B17" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C17" s="6">
+        <x:v>2919374.18</x:v>
+      </x:c>
+      <x:c r="D17" s="7">
+        <x:v>46254.0661014815</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:4">
+      <x:c r="A18" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B18" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C18" s="6">
+        <x:v>880241.67</x:v>
+      </x:c>
+      <x:c r="D18" s="7">
+        <x:v>46254.0661021296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:4">
+      <x:c r="A19" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B19" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C19" s="6">
+        <x:v>1085543.44</x:v>
+      </x:c>
+      <x:c r="D19" s="7">
+        <x:v>46254.0661027778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:4">
+      <x:c r="A20" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B20" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C20" s="6">
+        <x:v>138427.33</x:v>
+      </x:c>
+      <x:c r="D20" s="7">
+        <x:v>46254.0661033912</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:4">
+      <x:c r="A21" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B21" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C21" s="6">
+        <x:v>2955679.34</x:v>
+      </x:c>
+      <x:c r="D21" s="7">
+        <x:v>46254.0661039931</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:4">
+      <x:c r="A22" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B22" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C22" s="6">
+        <x:v>1140998.55</x:v>
+      </x:c>
+      <x:c r="D22" s="7">
+        <x:v>46254.0661045255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:4">
+      <x:c r="A23" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B23" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C23" s="6">
+        <x:v>1095131.7</x:v>
+      </x:c>
+      <x:c r="D23" s="7">
+        <x:v>46254.0661051852</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:4">
+      <x:c r="A24" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B24" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C24" s="6">
+        <x:v>2010855.35</x:v>
+      </x:c>
+      <x:c r="D24" s="7">
+        <x:v>46254.0661058218</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:4">
+      <x:c r="A25" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B25" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C25" s="6">
+        <x:v>514244.81</x:v>
+      </x:c>
+      <x:c r="D25" s="7">
+        <x:v>46254.0661063426</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:4">
+      <x:c r="A26" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B26" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C26" s="6">
+        <x:v>1138986.87</x:v>
+      </x:c>
+      <x:c r="D26" s="7">
+        <x:v>46254.0661068866</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:4">
+      <x:c r="A27" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B27" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C27" s="6">
+        <x:v>973523.92</x:v>
+      </x:c>
+      <x:c r="D27" s="7">
+        <x:v>46254.0661075579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:4">
+      <x:c r="A28" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B28" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C28" s="6">
+        <x:v>97268.63</x:v>
+      </x:c>
+      <x:c r="D28" s="7">
+        <x:v>46254.0661082986</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:4">
+      <x:c r="A29" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B29" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C29" s="6">
+        <x:v>199499.63</x:v>
+      </x:c>
+      <x:c r="D29" s="7">
+        <x:v>46254.0661090162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:4">
+      <x:c r="A30" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B30" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C30" s="6">
+        <x:v>944718.96</x:v>
+      </x:c>
+      <x:c r="D30" s="7">
+        <x:v>46254.0661099421</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:4">
+      <x:c r="A31" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B31" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C31" s="6">
+        <x:v>2743728.22</x:v>
+      </x:c>
+      <x:c r="D31" s="7">
+        <x:v>46254.0661108333</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:4">
+      <x:c r="A32" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B32" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C32" s="6">
+        <x:v>419751.33</x:v>
+      </x:c>
+      <x:c r="D32" s="7">
+        <x:v>46254.0661115394</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:4">
+      <x:c r="A33" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B33" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C33" s="6">
+        <x:v>2241294.42</x:v>
+      </x:c>
+      <x:c r="D33" s="7">
+        <x:v>46254.0661122454</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:4">
+      <x:c r="A34" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B34" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C34" s="6">
+        <x:v>1198802.11</x:v>
+      </x:c>
+      <x:c r="D34" s="7">
+        <x:v>46254.0661129282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:4">
+      <x:c r="A35" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B35" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C35" s="6">
+        <x:v>1481053.99</x:v>
+      </x:c>
+      <x:c r="D35" s="7">
+        <x:v>46254.0661134259</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:4">
+      <x:c r="A36" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B36" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C36" s="6">
+        <x:v>459371.12</x:v>
+      </x:c>
+      <x:c r="D36" s="7">
+        <x:v>46254.0661141319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:4">
+      <x:c r="A37" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B37" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C37" s="6">
+        <x:v>1267057.74</x:v>
+      </x:c>
+      <x:c r="D37" s="7">
+        <x:v>46254.066115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:4">
+      <x:c r="A38" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B38" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C38" s="6">
+        <x:v>1788069.4</x:v>
+      </x:c>
+      <x:c r="D38" s="7">
+        <x:v>46254.0661158796</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:4">
+      <x:c r="A39" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B39" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C39" s="6">
+        <x:v>2913264.05</x:v>
+      </x:c>
+      <x:c r="D39" s="7">
+        <x:v>46254.0661165625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:4">
+      <x:c r="A40" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B40" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C40" s="6">
+        <x:v>344540.68</x:v>
+      </x:c>
+      <x:c r="D40" s="7">
+        <x:v>46254.0661173495</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:4">
+      <x:c r="A41" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B41" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C41" s="6">
+        <x:v>2306027.6</x:v>
+      </x:c>
+      <x:c r="D41" s="7">
+        <x:v>46254.0661179745</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:4">
+      <x:c r="A42" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B42" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C42" s="6">
+        <x:v>1304860.99</x:v>
+      </x:c>
+      <x:c r="D42" s="7">
+        <x:v>46254.0661186343</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:4">
+      <x:c r="A43" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B43" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C43" s="6">
+        <x:v>2166554.09</x:v>
+      </x:c>
+      <x:c r="D43" s="7">
+        <x:v>46254.0661193982</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:4">
+      <x:c r="A44" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B44" s="5">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="C44" s="6">
+        <x:v>536776.99</x:v>
+      </x:c>
+      <x:c r="D44" s="7">
+        <x:v>46254.0661202546</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:4">
+      <x:c r="A45" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B45" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C45" s="6">
+        <x:v>896035.93</x:v>
+      </x:c>
+      <x:c r="D45" s="7">
+        <x:v>46254.0661211343</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:4">
+      <x:c r="A46" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B46" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C46" s="6">
+        <x:v>459364.97</x:v>
+      </x:c>
+      <x:c r="D46" s="7">
+        <x:v>46254.0661220255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:4">
+      <x:c r="A47" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B47" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C47" s="6">
+        <x:v>2336100.81</x:v>
+      </x:c>
+      <x:c r="D47" s="7">
+        <x:v>46254.0661228819</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:4">
+      <x:c r="A48" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B48" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C48" s="6">
+        <x:v>1797234.81</x:v>
+      </x:c>
+      <x:c r="D48" s="7">
+        <x:v>46254.0661236458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:4">
+      <x:c r="A49" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B49" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C49" s="6">
+        <x:v>2787366.75</x:v>
+      </x:c>
+      <x:c r="D49" s="7">
+        <x:v>46254.0661244213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:4">
+      <x:c r="A50" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B50" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C50" s="6">
+        <x:v>723373.91</x:v>
+      </x:c>
+      <x:c r="D50" s="7">
+        <x:v>46254.0661251157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:4">
+      <x:c r="A51" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B51" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C51" s="6">
+        <x:v>2195990.88</x:v>
+      </x:c>
+      <x:c r="D51" s="7">
+        <x:v>46254.0661260069</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:4">
+      <x:c r="A52" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B52" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C52" s="6">
+        <x:v>2297737.45</x:v>
+      </x:c>
+      <x:c r="D52" s="7">
+        <x:v>46254.0661267593</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:4">
+      <x:c r="A53" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B53" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C53" s="6">
+        <x:v>2840599.19</x:v>
+      </x:c>
+      <x:c r="D53" s="7">
+        <x:v>46254.0661275463</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:4">
+      <x:c r="A54" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B54" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C54" s="6">
+        <x:v>2617426.69</x:v>
+      </x:c>
+      <x:c r="D54" s="7">
+        <x:v>46254.0661285069</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:4">
+      <x:c r="A55" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B55" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C55" s="6">
+        <x:v>1618348.97</x:v>
+      </x:c>
+      <x:c r="D55" s="7">
+        <x:v>46254.0661292824</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:4">
+      <x:c r="A56" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B56" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C56" s="6">
+        <x:v>1197577.91</x:v>
+      </x:c>
+      <x:c r="D56" s="7">
+        <x:v>46254.0661300463</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:4">
+      <x:c r="A57" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B57" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C57" s="6">
+        <x:v>1553209.95</x:v>
+      </x:c>
+      <x:c r="D57" s="7">
+        <x:v>46254.0661307292</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:4">
+      <x:c r="A58" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B58" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C58" s="6">
+        <x:v>193013.66</x:v>
+      </x:c>
+      <x:c r="D58" s="7">
+        <x:v>46254.066131331</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:4">
+      <x:c r="A59" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B59" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C59" s="6">
+        <x:v>691114.08</x:v>
+      </x:c>
+      <x:c r="D59" s="7">
+        <x:v>46254.0661319792</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:4">
+      <x:c r="A60" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B60" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C60" s="6">
+        <x:v>2123815</x:v>
+      </x:c>
+      <x:c r="D60" s="7">
+        <x:v>46254.0661327199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:4">
+      <x:c r="A61" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B61" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C61" s="6">
+        <x:v>2716354.62</x:v>
+      </x:c>
+      <x:c r="D61" s="7">
+        <x:v>46254.0661333565</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:4">
+      <x:c r="A62" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B62" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C62" s="6">
+        <x:v>714775.9</x:v>
+      </x:c>
+      <x:c r="D62" s="7">
+        <x:v>46254.0661340278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:4">
+      <x:c r="A63" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B63" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C63" s="6">
+        <x:v>397803.23</x:v>
+      </x:c>
+      <x:c r="D63" s="7">
+        <x:v>46254.0661347685</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:4">
+      <x:c r="A64" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B64" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C64" s="6">
+        <x:v>729748.73</x:v>
+      </x:c>
+      <x:c r="D64" s="7">
+        <x:v>46254.0661354398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:4">
+      <x:c r="A65" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B65" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C65" s="6">
+        <x:v>572039.33</x:v>
+      </x:c>
+      <x:c r="D65" s="7">
+        <x:v>46254.0661360185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:4">
+      <x:c r="A66" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B66" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C66" s="6">
+        <x:v>1063538.4</x:v>
+      </x:c>
+      <x:c r="D66" s="7">
+        <x:v>46254.0661367361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:4">
+      <x:c r="A67" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B67" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C67" s="6">
+        <x:v>2187498.47</x:v>
+      </x:c>
+      <x:c r="D67" s="7">
+        <x:v>46254.0661374884</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:4">
+      <x:c r="A68" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B68" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C68" s="6">
+        <x:v>2184912.55</x:v>
+      </x:c>
+      <x:c r="D68" s="7">
+        <x:v>46254.0661383449</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:4">
+      <x:c r="A69" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B69" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C69" s="6">
+        <x:v>571436.52</x:v>
+      </x:c>
+      <x:c r="D69" s="7">
+        <x:v>46254.0661391782</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:4">
+      <x:c r="A70" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B70" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C70" s="6">
+        <x:v>551280.62</x:v>
+      </x:c>
+      <x:c r="D70" s="7">
+        <x:v>46254.0661398843</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:4">
+      <x:c r="A71" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B71" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C71" s="6">
+        <x:v>2769873.53</x:v>
+      </x:c>
+      <x:c r="D71" s="7">
+        <x:v>46254.0661407407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:4">
+      <x:c r="A72" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B72" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C72" s="6">
+        <x:v>2568044.71</x:v>
+      </x:c>
+      <x:c r="D72" s="7">
+        <x:v>46254.066141331</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:4">
+      <x:c r="A73" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B73" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C73" s="6">
+        <x:v>2997848.12</x:v>
+      </x:c>
+      <x:c r="D73" s="7">
+        <x:v>46254.066142037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:4">
+      <x:c r="A74" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B74" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C74" s="6">
+        <x:v>2260942.95</x:v>
+      </x:c>
+      <x:c r="D74" s="7">
+        <x:v>46254.0661428356</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:4">
+      <x:c r="A75" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B75" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C75" s="6">
+        <x:v>1457437.74</x:v>
+      </x:c>
+      <x:c r="D75" s="7">
+        <x:v>46254.0661435185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:4">
+      <x:c r="A76" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B76" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C76" s="6">
+        <x:v>2707426.15</x:v>
+      </x:c>
+      <x:c r="D76" s="7">
+        <x:v>46254.0661443403</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:4">
+      <x:c r="A77" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B77" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C77" s="6">
+        <x:v>2955941.22</x:v>
+      </x:c>
+      <x:c r="D77" s="7">
+        <x:v>46254.0661451042</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:4">
+      <x:c r="A78" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B78" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C78" s="6">
+        <x:v>2355602.94</x:v>
+      </x:c>
+      <x:c r="D78" s="7">
+        <x:v>46254.0661458102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:4">
+      <x:c r="A79" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B79" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C79" s="6">
+        <x:v>2871995.6</x:v>
+      </x:c>
+      <x:c r="D79" s="7">
+        <x:v>46254.0661465162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:4">
+      <x:c r="A80" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B80" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C80" s="6">
+        <x:v>1460527.56</x:v>
+      </x:c>
+      <x:c r="D80" s="7">
+        <x:v>46254.0661472338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:4">
+      <x:c r="A81" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B81" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C81" s="6">
+        <x:v>2906159.39</x:v>
+      </x:c>
+      <x:c r="D81" s="7">
+        <x:v>46254.0661480093</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:4">
+      <x:c r="A82" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B82" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C82" s="6">
+        <x:v>183811.76</x:v>
+      </x:c>
+      <x:c r="D82" s="7">
+        <x:v>46254.0661487847</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:4">
+      <x:c r="A83" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B83" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C83" s="6">
+        <x:v>1752948.61</x:v>
+      </x:c>
+      <x:c r="D83" s="7">
+        <x:v>46254.0661496296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:4">
+      <x:c r="A84" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B84" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C84" s="6">
+        <x:v>1593847.28</x:v>
+      </x:c>
+      <x:c r="D84" s="7">
+        <x:v>46254.0661505671</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:4">
+      <x:c r="A85" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B85" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C85" s="6">
+        <x:v>2554176.29</x:v>
+      </x:c>
+      <x:c r="D85" s="7">
+        <x:v>46254.0661514815</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:4">
+      <x:c r="A86" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B86" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C86" s="6">
+        <x:v>2025962.45</x:v>
+      </x:c>
+      <x:c r="D86" s="7">
+        <x:v>46254.0661524074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:4">
+      <x:c r="A87" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B87" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C87" s="6">
+        <x:v>2824846.79</x:v>
+      </x:c>
+      <x:c r="D87" s="7">
+        <x:v>46254.0661532292</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:4">
+      <x:c r="A88" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B88" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C88" s="6">
+        <x:v>1783962.94</x:v>
+      </x:c>
+      <x:c r="D88" s="7">
+        <x:v>46254.0661539815</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:4">
+      <x:c r="A89" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B89" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C89" s="6">
+        <x:v>1972462.12</x:v>
+      </x:c>
+      <x:c r="D89" s="7">
+        <x:v>46254.066154919</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:4">
+      <x:c r="A90" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B90" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C90" s="6">
+        <x:v>2804184.07</x:v>
+      </x:c>
+      <x:c r="D90" s="7">
+        <x:v>46254.0661556713</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:4">
+      <x:c r="A91" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B91" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C91" s="6">
+        <x:v>943237.4</x:v>
+      </x:c>
+      <x:c r="D91" s="7">
+        <x:v>46254.0661565046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:4">
+      <x:c r="A92" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B92" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C92" s="6">
+        <x:v>2015398.98</x:v>
+      </x:c>
+      <x:c r="D92" s="7">
+        <x:v>46254.0661573148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:4">
+      <x:c r="A93" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B93" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C93" s="6">
+        <x:v>2787125.98</x:v>
+      </x:c>
+      <x:c r="D93" s="7">
+        <x:v>46254.0661581829</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:4">
+      <x:c r="A94" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B94" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C94" s="6">
+        <x:v>1863856.61</x:v>
+      </x:c>
+      <x:c r="D94" s="7">
+        <x:v>46254.0661591088</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:4">
+      <x:c r="A95" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B95" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C95" s="6">
+        <x:v>1613365.58</x:v>
+      </x:c>
+      <x:c r="D95" s="7">
+        <x:v>46254.0661599653</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:4">
+      <x:c r="A96" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B96" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C96" s="6">
+        <x:v>2799844.87</x:v>
+      </x:c>
+      <x:c r="D96" s="7">
+        <x:v>46254.0661607755</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:4">
+      <x:c r="A97" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B97" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C97" s="6">
+        <x:v>1109211.74</x:v>
+      </x:c>
+      <x:c r="D97" s="7">
+        <x:v>46254.066161713</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:4">
+      <x:c r="A98" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B98" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C98" s="6">
+        <x:v>1630110.67</x:v>
+      </x:c>
+      <x:c r="D98" s="7">
+        <x:v>46254.066162581</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:4">
+      <x:c r="A99" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B99" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C99" s="6">
+        <x:v>1962274.98</x:v>
+      </x:c>
+      <x:c r="D99" s="7">
+        <x:v>46254.0661637847</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:4">
+      <x:c r="A100" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B100" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C100" s="6">
+        <x:v>1664252.25</x:v>
+      </x:c>
+      <x:c r="D100" s="7">
+        <x:v>46254.0661646181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:4">
+      <x:c r="A101" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B101" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C101" s="6">
+        <x:v>794133.3</x:v>
+      </x:c>
+      <x:c r="D101" s="7">
+        <x:v>46254.0661654514</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:4">
+      <x:c r="A102" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B102" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C102" s="6">
+        <x:v>467188.28</x:v>
+      </x:c>
+      <x:c r="D102" s="7">
+        <x:v>46254.0661662384</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:autoFilter ref="A1:D1"/>

--- a/wwwroot/CheckPrintTracking/Check_Print_Tracking_v1.xlsx
+++ b/wwwroot/CheckPrintTracking/Check_Print_Tracking_v1.xlsx
@@ -2133,6 +2133,1406 @@
         <x:v>46254.0661662384</x:v>
       </x:c>
     </x:row>
+    <x:row r="103" spans="1:4">
+      <x:c r="A103" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B103" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C103" s="6">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="D103" s="7">
+        <x:v>46254.0745016204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:4">
+      <x:c r="A104" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B104" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C104" s="6">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="D104" s="7">
+        <x:v>46254.0745125116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:4">
+      <x:c r="A105" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B105" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C105" s="6">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D105" s="7">
+        <x:v>46254.0745142014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:4">
+      <x:c r="A106" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B106" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C106" s="6">
+        <x:v>825812.93</x:v>
+      </x:c>
+      <x:c r="D106" s="7">
+        <x:v>46254.0745160301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:4">
+      <x:c r="A107" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B107" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C107" s="6">
+        <x:v>308383.03</x:v>
+      </x:c>
+      <x:c r="D107" s="7">
+        <x:v>46254.074517581</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:4">
+      <x:c r="A108" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B108" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C108" s="6">
+        <x:v>1266343.54</x:v>
+      </x:c>
+      <x:c r="D108" s="7">
+        <x:v>46254.0745193287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:4">
+      <x:c r="A109" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B109" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C109" s="6">
+        <x:v>698750.02</x:v>
+      </x:c>
+      <x:c r="D109" s="7">
+        <x:v>46254.0745208218</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:4">
+      <x:c r="A110" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B110" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C110" s="6">
+        <x:v>597314.11</x:v>
+      </x:c>
+      <x:c r="D110" s="7">
+        <x:v>46254.0745224306</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:4">
+      <x:c r="A111" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B111" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C111" s="6">
+        <x:v>1348177.93</x:v>
+      </x:c>
+      <x:c r="D111" s="7">
+        <x:v>46254.0745239236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:4">
+      <x:c r="A112" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B112" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C112" s="6">
+        <x:v>20489.78</x:v>
+      </x:c>
+      <x:c r="D112" s="7">
+        <x:v>46254.0745255093</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:4">
+      <x:c r="A113" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B113" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C113" s="6">
+        <x:v>1021411.3</x:v>
+      </x:c>
+      <x:c r="D113" s="7">
+        <x:v>46254.0745270486</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:4">
+      <x:c r="A114" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B114" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C114" s="6">
+        <x:v>2290718.89</x:v>
+      </x:c>
+      <x:c r="D114" s="7">
+        <x:v>46254.0745283449</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:4">
+      <x:c r="A115" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B115" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C115" s="6">
+        <x:v>291052.41</x:v>
+      </x:c>
+      <x:c r="D115" s="7">
+        <x:v>46254.0745297917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:4">
+      <x:c r="A116" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B116" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C116" s="6">
+        <x:v>2421577.69</x:v>
+      </x:c>
+      <x:c r="D116" s="7">
+        <x:v>46254.07453125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:4">
+      <x:c r="A117" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B117" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C117" s="6">
+        <x:v>2919374.18</x:v>
+      </x:c>
+      <x:c r="D117" s="7">
+        <x:v>46254.0745326389</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:4">
+      <x:c r="A118" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B118" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C118" s="6">
+        <x:v>880241.67</x:v>
+      </x:c>
+      <x:c r="D118" s="7">
+        <x:v>46254.0745342245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:4">
+      <x:c r="A119" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B119" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C119" s="6">
+        <x:v>1085543.44</x:v>
+      </x:c>
+      <x:c r="D119" s="7">
+        <x:v>46254.0745355787</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:4">
+      <x:c r="A120" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B120" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C120" s="6">
+        <x:v>138427.33</x:v>
+      </x:c>
+      <x:c r="D120" s="7">
+        <x:v>46254.0745367361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:4">
+      <x:c r="A121" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B121" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C121" s="6">
+        <x:v>2955679.34</x:v>
+      </x:c>
+      <x:c r="D121" s="7">
+        <x:v>46254.0745380671</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:4">
+      <x:c r="A122" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B122" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C122" s="6">
+        <x:v>1140998.55</x:v>
+      </x:c>
+      <x:c r="D122" s="7">
+        <x:v>46254.0745397222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:4">
+      <x:c r="A123" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B123" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C123" s="6">
+        <x:v>1095131.7</x:v>
+      </x:c>
+      <x:c r="D123" s="7">
+        <x:v>46254.0745411111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:4">
+      <x:c r="A124" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B124" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C124" s="6">
+        <x:v>2010855.35</x:v>
+      </x:c>
+      <x:c r="D124" s="7">
+        <x:v>46254.0745425232</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:4">
+      <x:c r="A125" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B125" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C125" s="6">
+        <x:v>514244.81</x:v>
+      </x:c>
+      <x:c r="D125" s="7">
+        <x:v>46254.0745437963</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:4">
+      <x:c r="A126" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B126" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C126" s="6">
+        <x:v>1138986.87</x:v>
+      </x:c>
+      <x:c r="D126" s="7">
+        <x:v>46254.0745449306</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:4">
+      <x:c r="A127" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B127" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C127" s="6">
+        <x:v>973523.92</x:v>
+      </x:c>
+      <x:c r="D127" s="7">
+        <x:v>46254.0745462732</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:4">
+      <x:c r="A128" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B128" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C128" s="6">
+        <x:v>97268.63</x:v>
+      </x:c>
+      <x:c r="D128" s="7">
+        <x:v>46254.0745477315</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:4">
+      <x:c r="A129" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B129" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C129" s="6">
+        <x:v>199499.63</x:v>
+      </x:c>
+      <x:c r="D129" s="7">
+        <x:v>46254.0745488194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:4">
+      <x:c r="A130" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B130" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C130" s="6">
+        <x:v>944718.96</x:v>
+      </x:c>
+      <x:c r="D130" s="7">
+        <x:v>46254.074549838</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:4">
+      <x:c r="A131" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B131" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C131" s="6">
+        <x:v>2743728.22</x:v>
+      </x:c>
+      <x:c r="D131" s="7">
+        <x:v>46254.074551331</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:4">
+      <x:c r="A132" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B132" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C132" s="6">
+        <x:v>419751.33</x:v>
+      </x:c>
+      <x:c r="D132" s="7">
+        <x:v>46254.0745527315</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:4">
+      <x:c r="A133" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B133" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C133" s="6">
+        <x:v>2241294.42</x:v>
+      </x:c>
+      <x:c r="D133" s="7">
+        <x:v>46254.0745539583</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:4">
+      <x:c r="A134" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B134" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C134" s="6">
+        <x:v>1198802.11</x:v>
+      </x:c>
+      <x:c r="D134" s="7">
+        <x:v>46254.0745551157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:4">
+      <x:c r="A135" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B135" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C135" s="6">
+        <x:v>1481053.99</x:v>
+      </x:c>
+      <x:c r="D135" s="7">
+        <x:v>46254.074556169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:4">
+      <x:c r="A136" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B136" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C136" s="6">
+        <x:v>459371.12</x:v>
+      </x:c>
+      <x:c r="D136" s="7">
+        <x:v>46254.0745573032</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:4">
+      <x:c r="A137" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B137" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C137" s="6">
+        <x:v>1267057.74</x:v>
+      </x:c>
+      <x:c r="D137" s="7">
+        <x:v>46254.0745589005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:4">
+      <x:c r="A138" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B138" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C138" s="6">
+        <x:v>1788069.4</x:v>
+      </x:c>
+      <x:c r="D138" s="7">
+        <x:v>46254.0745604167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:4">
+      <x:c r="A139" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B139" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C139" s="6">
+        <x:v>2913264.05</x:v>
+      </x:c>
+      <x:c r="D139" s="7">
+        <x:v>46254.0745614468</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:4">
+      <x:c r="A140" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B140" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C140" s="6">
+        <x:v>344540.68</x:v>
+      </x:c>
+      <x:c r="D140" s="7">
+        <x:v>46254.0745628241</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:4">
+      <x:c r="A141" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B141" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C141" s="6">
+        <x:v>2306027.6</x:v>
+      </x:c>
+      <x:c r="D141" s="7">
+        <x:v>46254.0745642245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:4">
+      <x:c r="A142" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B142" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C142" s="6">
+        <x:v>1304860.99</x:v>
+      </x:c>
+      <x:c r="D142" s="7">
+        <x:v>46254.0745656366</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:4">
+      <x:c r="A143" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B143" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C143" s="6">
+        <x:v>2166554.09</x:v>
+      </x:c>
+      <x:c r="D143" s="7">
+        <x:v>46254.0745668866</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:4">
+      <x:c r="A144" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B144" s="5">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="C144" s="6">
+        <x:v>536776.99</x:v>
+      </x:c>
+      <x:c r="D144" s="7">
+        <x:v>46254.0745682407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:4">
+      <x:c r="A145" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B145" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C145" s="6">
+        <x:v>896035.93</x:v>
+      </x:c>
+      <x:c r="D145" s="7">
+        <x:v>46254.0745698148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:4">
+      <x:c r="A146" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B146" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C146" s="6">
+        <x:v>459364.97</x:v>
+      </x:c>
+      <x:c r="D146" s="7">
+        <x:v>46254.0745714699</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:4">
+      <x:c r="A147" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B147" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C147" s="6">
+        <x:v>2336100.81</x:v>
+      </x:c>
+      <x:c r="D147" s="7">
+        <x:v>46254.0745726852</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:4">
+      <x:c r="A148" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B148" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C148" s="6">
+        <x:v>1797234.81</x:v>
+      </x:c>
+      <x:c r="D148" s="7">
+        <x:v>46254.0745740741</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:4">
+      <x:c r="A149" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B149" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C149" s="6">
+        <x:v>2787366.75</x:v>
+      </x:c>
+      <x:c r="D149" s="7">
+        <x:v>46254.0745755671</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:4">
+      <x:c r="A150" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B150" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C150" s="6">
+        <x:v>723373.91</x:v>
+      </x:c>
+      <x:c r="D150" s="7">
+        <x:v>46254.074577037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:4">
+      <x:c r="A151" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B151" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C151" s="6">
+        <x:v>2195990.88</x:v>
+      </x:c>
+      <x:c r="D151" s="7">
+        <x:v>46254.0745790393</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:4">
+      <x:c r="A152" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B152" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C152" s="6">
+        <x:v>2297737.45</x:v>
+      </x:c>
+      <x:c r="D152" s="7">
+        <x:v>46254.0745802315</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:4">
+      <x:c r="A153" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B153" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C153" s="6">
+        <x:v>2840599.19</x:v>
+      </x:c>
+      <x:c r="D153" s="7">
+        <x:v>46254.0745817245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:4">
+      <x:c r="A154" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B154" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C154" s="6">
+        <x:v>2617426.69</x:v>
+      </x:c>
+      <x:c r="D154" s="7">
+        <x:v>46254.0745832292</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:4">
+      <x:c r="A155" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B155" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C155" s="6">
+        <x:v>1618348.97</x:v>
+      </x:c>
+      <x:c r="D155" s="7">
+        <x:v>46254.0745844213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:4">
+      <x:c r="A156" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B156" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C156" s="6">
+        <x:v>1197577.91</x:v>
+      </x:c>
+      <x:c r="D156" s="7">
+        <x:v>46254.0745859606</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:4">
+      <x:c r="A157" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B157" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C157" s="6">
+        <x:v>1553209.95</x:v>
+      </x:c>
+      <x:c r="D157" s="7">
+        <x:v>46254.074587419</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:4">
+      <x:c r="A158" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B158" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C158" s="6">
+        <x:v>193013.66</x:v>
+      </x:c>
+      <x:c r="D158" s="7">
+        <x:v>46254.0745887847</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:4">
+      <x:c r="A159" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B159" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C159" s="6">
+        <x:v>691114.08</x:v>
+      </x:c>
+      <x:c r="D159" s="7">
+        <x:v>46254.0745899074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:4">
+      <x:c r="A160" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B160" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C160" s="6">
+        <x:v>2123815</x:v>
+      </x:c>
+      <x:c r="D160" s="7">
+        <x:v>46254.074591169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:4">
+      <x:c r="A161" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B161" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C161" s="6">
+        <x:v>2716354.62</x:v>
+      </x:c>
+      <x:c r="D161" s="7">
+        <x:v>46254.074592662</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:4">
+      <x:c r="A162" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B162" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C162" s="6">
+        <x:v>714775.9</x:v>
+      </x:c>
+      <x:c r="D162" s="7">
+        <x:v>46254.0745937847</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:4">
+      <x:c r="A163" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B163" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C163" s="6">
+        <x:v>397803.23</x:v>
+      </x:c>
+      <x:c r="D163" s="7">
+        <x:v>46254.0745949306</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:4">
+      <x:c r="A164" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B164" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C164" s="6">
+        <x:v>729748.73</x:v>
+      </x:c>
+      <x:c r="D164" s="7">
+        <x:v>46254.0745961806</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:4">
+      <x:c r="A165" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B165" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C165" s="6">
+        <x:v>572039.33</x:v>
+      </x:c>
+      <x:c r="D165" s="7">
+        <x:v>46254.0745970255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:4">
+      <x:c r="A166" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B166" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C166" s="6">
+        <x:v>1063538.4</x:v>
+      </x:c>
+      <x:c r="D166" s="7">
+        <x:v>46254.0745981597</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:4">
+      <x:c r="A167" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B167" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C167" s="6">
+        <x:v>2187498.47</x:v>
+      </x:c>
+      <x:c r="D167" s="7">
+        <x:v>46254.0745990509</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:4">
+      <x:c r="A168" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B168" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C168" s="6">
+        <x:v>2184912.55</x:v>
+      </x:c>
+      <x:c r="D168" s="7">
+        <x:v>46254.0745998148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:4">
+      <x:c r="A169" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B169" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C169" s="6">
+        <x:v>571436.52</x:v>
+      </x:c>
+      <x:c r="D169" s="7">
+        <x:v>46254.0746007986</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:4">
+      <x:c r="A170" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B170" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C170" s="6">
+        <x:v>551280.62</x:v>
+      </x:c>
+      <x:c r="D170" s="7">
+        <x:v>46254.0746015394</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:4">
+      <x:c r="A171" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B171" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C171" s="6">
+        <x:v>2769873.53</x:v>
+      </x:c>
+      <x:c r="D171" s="7">
+        <x:v>46254.0746024769</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:4">
+      <x:c r="A172" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B172" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C172" s="6">
+        <x:v>2568044.71</x:v>
+      </x:c>
+      <x:c r="D172" s="7">
+        <x:v>46254.0746034375</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:4">
+      <x:c r="A173" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B173" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C173" s="6">
+        <x:v>2997848.12</x:v>
+      </x:c>
+      <x:c r="D173" s="7">
+        <x:v>46254.0746046181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:4">
+      <x:c r="A174" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B174" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C174" s="6">
+        <x:v>2260942.95</x:v>
+      </x:c>
+      <x:c r="D174" s="7">
+        <x:v>46254.0746055787</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:4">
+      <x:c r="A175" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B175" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C175" s="6">
+        <x:v>1457437.74</x:v>
+      </x:c>
+      <x:c r="D175" s="7">
+        <x:v>46254.0746066088</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:4">
+      <x:c r="A176" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B176" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C176" s="6">
+        <x:v>2707426.15</x:v>
+      </x:c>
+      <x:c r="D176" s="7">
+        <x:v>46254.0746076389</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:4">
+      <x:c r="A177" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B177" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C177" s="6">
+        <x:v>2955941.22</x:v>
+      </x:c>
+      <x:c r="D177" s="7">
+        <x:v>46254.0746085532</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:4">
+      <x:c r="A178" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B178" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C178" s="6">
+        <x:v>2355602.94</x:v>
+      </x:c>
+      <x:c r="D178" s="7">
+        <x:v>46254.0746097917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:4">
+      <x:c r="A179" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B179" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C179" s="6">
+        <x:v>2871995.6</x:v>
+      </x:c>
+      <x:c r="D179" s="7">
+        <x:v>46254.074610787</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:4">
+      <x:c r="A180" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B180" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C180" s="6">
+        <x:v>1460527.56</x:v>
+      </x:c>
+      <x:c r="D180" s="7">
+        <x:v>46254.0746116667</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:4">
+      <x:c r="A181" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B181" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C181" s="6">
+        <x:v>2906159.39</x:v>
+      </x:c>
+      <x:c r="D181" s="7">
+        <x:v>46254.0746125347</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:4">
+      <x:c r="A182" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B182" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C182" s="6">
+        <x:v>183811.76</x:v>
+      </x:c>
+      <x:c r="D182" s="7">
+        <x:v>46254.0746133333</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:4">
+      <x:c r="A183" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B183" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C183" s="6">
+        <x:v>1752948.61</x:v>
+      </x:c>
+      <x:c r="D183" s="7">
+        <x:v>46254.0746142361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:4">
+      <x:c r="A184" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B184" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C184" s="6">
+        <x:v>1593847.28</x:v>
+      </x:c>
+      <x:c r="D184" s="7">
+        <x:v>46254.0746152431</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:4">
+      <x:c r="A185" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B185" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C185" s="6">
+        <x:v>2554176.29</x:v>
+      </x:c>
+      <x:c r="D185" s="7">
+        <x:v>46254.0746163079</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:4">
+      <x:c r="A186" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B186" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C186" s="6">
+        <x:v>2025962.45</x:v>
+      </x:c>
+      <x:c r="D186" s="7">
+        <x:v>46254.0746171875</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:4">
+      <x:c r="A187" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B187" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C187" s="6">
+        <x:v>2824846.79</x:v>
+      </x:c>
+      <x:c r="D187" s="7">
+        <x:v>46254.0746185185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:4">
+      <x:c r="A188" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B188" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C188" s="6">
+        <x:v>1783962.94</x:v>
+      </x:c>
+      <x:c r="D188" s="7">
+        <x:v>46254.074619375</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:4">
+      <x:c r="A189" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B189" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C189" s="6">
+        <x:v>1972462.12</x:v>
+      </x:c>
+      <x:c r="D189" s="7">
+        <x:v>46254.0746201968</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:4">
+      <x:c r="A190" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B190" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C190" s="6">
+        <x:v>2804184.07</x:v>
+      </x:c>
+      <x:c r="D190" s="7">
+        <x:v>46254.0746210301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:4">
+      <x:c r="A191" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B191" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C191" s="6">
+        <x:v>943237.4</x:v>
+      </x:c>
+      <x:c r="D191" s="7">
+        <x:v>46254.0746218056</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:4">
+      <x:c r="A192" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B192" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C192" s="6">
+        <x:v>2015398.98</x:v>
+      </x:c>
+      <x:c r="D192" s="7">
+        <x:v>46254.0746224884</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:4">
+      <x:c r="A193" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B193" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C193" s="6">
+        <x:v>2787125.98</x:v>
+      </x:c>
+      <x:c r="D193" s="7">
+        <x:v>46254.0746233565</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:4">
+      <x:c r="A194" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B194" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C194" s="6">
+        <x:v>1863856.61</x:v>
+      </x:c>
+      <x:c r="D194" s="7">
+        <x:v>46254.0746241088</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:4">
+      <x:c r="A195" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B195" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C195" s="6">
+        <x:v>1613365.58</x:v>
+      </x:c>
+      <x:c r="D195" s="7">
+        <x:v>46254.0746252778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:4">
+      <x:c r="A196" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B196" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C196" s="6">
+        <x:v>2799844.87</x:v>
+      </x:c>
+      <x:c r="D196" s="7">
+        <x:v>46254.0746260995</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:4">
+      <x:c r="A197" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B197" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C197" s="6">
+        <x:v>1109211.74</x:v>
+      </x:c>
+      <x:c r="D197" s="7">
+        <x:v>46254.0746268056</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:4">
+      <x:c r="A198" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B198" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C198" s="6">
+        <x:v>1630110.67</x:v>
+      </x:c>
+      <x:c r="D198" s="7">
+        <x:v>46254.0746278819</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" spans="1:4">
+      <x:c r="A199" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B199" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C199" s="6">
+        <x:v>1962274.98</x:v>
+      </x:c>
+      <x:c r="D199" s="7">
+        <x:v>46254.0746291435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" spans="1:4">
+      <x:c r="A200" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B200" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C200" s="6">
+        <x:v>1664252.25</x:v>
+      </x:c>
+      <x:c r="D200" s="7">
+        <x:v>46254.0746301968</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" spans="1:4">
+      <x:c r="A201" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B201" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C201" s="6">
+        <x:v>794133.3</x:v>
+      </x:c>
+      <x:c r="D201" s="7">
+        <x:v>46254.0746309491</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" spans="1:4">
+      <x:c r="A202" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B202" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C202" s="6">
+        <x:v>467188.28</x:v>
+      </x:c>
+      <x:c r="D202" s="7">
+        <x:v>46254.0746316435</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:autoFilter ref="A1:D1"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/wwwroot/CheckPrintTracking/Check_Print_Tracking_v1.xlsx
+++ b/wwwroot/CheckPrintTracking/Check_Print_Tracking_v1.xlsx
@@ -3533,6 +3533,20 @@
         <x:v>46254.0746316435</x:v>
       </x:c>
     </x:row>
+    <x:row r="203" spans="1:4">
+      <x:c r="A203" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B203" s="5">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="C203" s="6">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="D203" s="7">
+        <x:v>46254.0822333102</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:autoFilter ref="A1:D1"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
